--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0236.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0236.xlsx
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Nhạc nền ban ngày của Rừng Bjartr.</t>
+          <t>Nhạc nền ban ngày của Bjartr Woods.</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Nhạc nền đêm khuya tại Rừng Bjartr.</t>
+          <t>Nhạc nền đêm khuya tại Bjartr Woods.</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Throttle Up!</t>
+          <t>Tăng Tốc Nào!</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Every Ngày A Carnival (Bản Remix)</t>
+          <t>Every Day A Carnival (Bản Remix)</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Chỉ cần biết ngươi ở đây thôi là ta đã thấy mình bất khả chiến bại rồi.</t>
+          <t>Chỉ cần biết mày ở đây thôi là tao đã thấy mình bất khả chiến bại rồi.</t>
         </is>
       </c>
     </row>
@@ -10470,7 +10470,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Cung cấp một Echo hạng Cao Cấp mà bạn đã mở khóa</t>
+          <t>Cung cấp một Echo cấp Tinh Anh mà bạn đã mở khóa</t>
         </is>
       </c>
     </row>
